--- a/data/trans_orig/RUIDO_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan el ruido en su municipio o lugar de residencia en 2023</t>
+          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan el ruido en su municipio o lugar de residencia en 2023 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25255</t>
+          <t>25647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68466</t>
+          <t>67582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24704</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34575</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84568</t>
+          <t>84440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56060</t>
+          <t>57448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34935</t>
+          <t>34703</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>62487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63400</t>
+          <t>63227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107750</t>
+          <t>107657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43390</t>
+          <t>42621</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13683</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35358</t>
+          <t>35601</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33758</t>
+          <t>31765</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69061</t>
+          <t>67443</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27497</t>
+          <t>28495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40692</t>
+          <t>39594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>25942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>14557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40286</t>
+          <t>42045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24433</t>
+          <t>25310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25778</t>
+          <t>25502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>44018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35980</t>
+          <t>34447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39530</t>
+          <t>40416</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36911</t>
+          <t>36912</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65064</t>
+          <t>66918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38209</t>
+          <t>36847</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65244</t>
+          <t>65705</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46664</t>
+          <t>46663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70199</t>
+          <t>72235</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91062</t>
+          <t>91006</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>128292</t>
+          <t>129196</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41398</t>
+          <t>40663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>17222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36257</t>
+          <t>36198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39119</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70179</t>
+          <t>70093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31766</t>
+          <t>32148</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>15619</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34885</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58005</t>
+          <t>58236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21017</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22459</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39296</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33193</t>
+          <t>33521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57798</t>
+          <t>58880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34925</t>
+          <t>35373</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53949</t>
+          <t>54654</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>74907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104098</t>
+          <t>107133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89170</t>
+          <t>88528</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>118932</t>
+          <t>118145</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68899</t>
+          <t>70712</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91543</t>
+          <t>93669</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>166082</t>
+          <t>166089</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>203531</t>
+          <t>203262</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20654</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41353</t>
+          <t>42416</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35644</t>
+          <t>35303</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44323</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71428</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36907</t>
+          <t>35926</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>16010</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31297</t>
+          <t>30185</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36657</t>
+          <t>37518</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61741</t>
+          <t>60839</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32232</t>
+          <t>31906</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18138</t>
+          <t>18944</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33824</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,42 +2826,42 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>13,49%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>45582</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>35777</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>59657</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>7,14%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>45582</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>34598</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>59636</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40643</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68330</t>
+          <t>68464</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36722</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56854</t>
+          <t>57205</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>85192</t>
+          <t>85029</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>118657</t>
+          <t>117462</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>101996</t>
+          <t>101448</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>137327</t>
+          <t>136758</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>86134</t>
+          <t>84264</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109422</t>
+          <t>107970</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>194787</t>
+          <t>192850</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>238040</t>
+          <t>238171</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25552</t>
+          <t>25619</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48523</t>
+          <t>48012</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36435</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55260</t>
+          <t>56345</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68377</t>
+          <t>66440</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95996</t>
+          <t>96114</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27664</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30184</t>
+          <t>30481</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48690</t>
+          <t>48530</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45869</t>
+          <t>47753</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71376</t>
+          <t>72367</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24235</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11353</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23265</t>
+          <t>23045</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>43300</t>
+          <t>43354</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>51235</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>74897</t>
+          <t>78147</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>59004</t>
+          <t>57106</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79833</t>
+          <t>78870</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>112604</t>
+          <t>113895</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>145853</t>
+          <t>147139</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>81203</t>
+          <t>78632</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108376</t>
+          <t>107156</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67405</t>
+          <t>67603</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>88994</t>
+          <t>89008</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>155147</t>
+          <t>154272</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>190194</t>
+          <t>189241</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>26427</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47021</t>
+          <t>47253</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19189</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>33242</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>48271</t>
+          <t>49418</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>73877</t>
+          <t>74301</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>27720</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>47958</t>
+          <t>47596</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29236</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45457</t>
+          <t>44602</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>61266</t>
+          <t>59799</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>88020</t>
+          <t>85518</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15628</t>
+          <t>15457</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>45706</t>
+          <t>47448</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>51707</t>
+          <t>51656</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>24142</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40301</t>
+          <t>40447</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>115820</t>
+          <t>114076</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>336448</t>
+          <t>339643</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>132267</t>
+          <t>133226</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>435012</t>
+          <t>434118</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,03%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>50641</t>
+          <t>50560</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>70482</t>
+          <t>70360</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>114222</t>
+          <t>113866</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>37531</t>
+          <t>39873</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>185216</t>
+          <t>185591</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>18569</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>32902</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>48554</t>
+          <t>47959</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>79600</t>
+          <t>79217</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>34893</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>58161</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>90027</t>
+          <t>90524</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23400</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>23066</t>
+          <t>23642</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>39787</t>
+          <t>40067</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>26114</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>41417</t>
+          <t>42683</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>88503</t>
+          <t>87905</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>107801</t>
+          <t>108439</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>119434</t>
+          <t>119729</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>145206</t>
+          <t>145690</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>29103</t>
+          <t>28836</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>44994</t>
+          <t>45570</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>36989</t>
+          <t>36125</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>54210</t>
+          <t>53994</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>70991</t>
+          <t>70183</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>95586</t>
+          <t>94461</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>9800</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>21339</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>26799</t>
+          <t>26259</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>26985</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>43724</t>
+          <t>43793</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26799</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>16856</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>34553</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>51821</t>
+          <t>51623</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>99971</t>
+          <t>100104</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>163995</t>
+          <t>167002</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>75302</t>
+          <t>72979</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>149638</t>
+          <t>151828</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>195872</t>
+          <t>195522</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>296553</t>
+          <t>296322</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>248583</t>
+          <t>252177</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>313491</t>
+          <t>317602</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>440661</t>
+          <t>439397</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>913501</t>
+          <t>890283</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>710318</t>
+          <t>709346</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1333496</t>
+          <t>1353989</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>450314</t>
+          <t>452150</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>527014</t>
+          <t>531702</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>282932</t>
+          <t>278057</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>508186</t>
+          <t>506462</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>702130</t>
+          <t>692803</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1014349</t>
+          <t>1011986</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>159317</t>
+          <t>160164</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>211053</t>
+          <t>212122</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>111439</t>
+          <t>111466</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>208890</t>
+          <t>212570</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>270599</t>
+          <t>278263</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>400077</t>
+          <t>401916</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>133150</t>
+          <t>135529</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>182691</t>
+          <t>184790</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>112928</t>
+          <t>120102</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>219008</t>
+          <t>219843</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>264235</t>
+          <t>260708</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>379795</t>
+          <t>384272</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44720</t>
+          <t>40852</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25647</t>
+          <t>23361</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67582</t>
+          <t>60638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25712</t>
+          <t>30351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57473</t>
+          <t>56563</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36830</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84440</t>
+          <t>82428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>38884</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20949</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57448</t>
+          <t>57385</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48605</t>
+          <t>59611</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>43715</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62487</t>
+          <t>76403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>84303</t>
+          <t>98494</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63227</t>
+          <t>76571</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107657</t>
+          <t>122042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25446</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>14437</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42621</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>23447</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35601</t>
+          <t>37311</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>48669</t>
+          <t>48680</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31765</t>
+          <t>33745</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67443</t>
+          <t>68455</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28495</t>
+          <t>31451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>22057</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>25266</t>
+          <t>28557</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13856</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39594</t>
+          <t>46864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>26133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14231</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25015</t>
+          <t>30655</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>24227</t>
+          <t>30411</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42045</t>
+          <t>47121</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>130843</t>
+          <t>134235</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>130843</t>
+          <t>134235</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>130843</t>
+          <t>134235</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>109095</t>
+          <t>128470</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109095</t>
+          <t>128470</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>109095</t>
+          <t>128470</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>239938</t>
+          <t>262705</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>239938</t>
+          <t>262705</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>239938</t>
+          <t>262705</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25310</t>
+          <t>25064</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25502</t>
+          <t>29672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>30900</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44018</t>
+          <t>45444</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>29849</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34447</t>
+          <t>43733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29045</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>27048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40416</t>
+          <t>50562</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>50289</t>
+          <t>67932</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36912</t>
+          <t>51881</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66918</t>
+          <t>85865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50928</t>
+          <t>57431</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36847</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65705</t>
+          <t>73678</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58740</t>
+          <t>60865</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46663</t>
+          <t>49050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72235</t>
+          <t>74394</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>109668</t>
+          <t>118296</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91006</t>
+          <t>99372</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129196</t>
+          <t>140789</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16711</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40663</t>
+          <t>42554</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25079</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36198</t>
+          <t>38480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>53121</t>
+          <t>55953</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39364</t>
+          <t>41743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70093</t>
+          <t>76399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32148</t>
+          <t>35640</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24150</t>
+          <t>29225</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>41484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>42591</t>
+          <t>49990</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30607</t>
+          <t>35590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58236</t>
+          <t>66406</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>131707</t>
+          <t>149880</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131707</t>
+          <t>149880</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>131707</t>
+          <t>149880</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>152658</t>
+          <t>173191</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>152658</t>
+          <t>173191</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>152658</t>
+          <t>173191</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>284365</t>
+          <t>323071</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>284365</t>
+          <t>323071</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>284365</t>
+          <t>323071</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12042</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>20880</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>26276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>27007</t>
+          <t>30216</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>43118</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44537</t>
+          <t>59273</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33521</t>
+          <t>45158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58880</t>
+          <t>74877</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44039</t>
+          <t>55253</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35373</t>
+          <t>45722</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54654</t>
+          <t>66989</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>88576</t>
+          <t>114527</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74907</t>
+          <t>98678</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107133</t>
+          <t>134993</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103595</t>
+          <t>112198</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88528</t>
+          <t>97038</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>118145</t>
+          <t>129372</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80336</t>
+          <t>88648</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70712</t>
+          <t>76121</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>93669</t>
+          <t>100369</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>183932</t>
+          <t>200845</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>166089</t>
+          <t>182560</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>203262</t>
+          <t>221677</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>35203</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20694</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42416</t>
+          <t>48211</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19186</t>
+          <t>21060</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35303</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>57255</t>
+          <t>64668</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>50934</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70046</t>
+          <t>80386</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>29813</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35926</t>
+          <t>42274</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16010</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30185</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>48037</t>
+          <t>54739</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>42259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60839</t>
+          <t>68715</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>215894</t>
+          <t>248529</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>215894</t>
+          <t>248529</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>215894</t>
+          <t>248529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>188912</t>
+          <t>216466</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>188912</t>
+          <t>216466</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>188912</t>
+          <t>216466</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>404807</t>
+          <t>464995</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>404807</t>
+          <t>464995</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>404807</t>
+          <t>464995</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20521</t>
+          <t>21010</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31906</t>
+          <t>32598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>26806</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18944</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34281</t>
+          <t>35990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>45582</t>
+          <t>47817</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>36372</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59657</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>53467</t>
+          <t>63041</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>48655</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68464</t>
+          <t>78753</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>47205</t>
+          <t>53279</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>42943</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57205</t>
+          <t>63462</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>100672</t>
+          <t>116320</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>85029</t>
+          <t>101072</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>117462</t>
+          <t>133643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118051</t>
+          <t>115250</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>101448</t>
+          <t>98715</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>136758</t>
+          <t>132352</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>96636</t>
+          <t>102056</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>84264</t>
+          <t>90317</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>107970</t>
+          <t>116284</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>214687</t>
+          <t>217306</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>192850</t>
+          <t>198856</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>238171</t>
+          <t>239328</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35501</t>
+          <t>37796</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25619</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48012</t>
+          <t>50432</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>46172</t>
+          <t>50295</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36950</t>
+          <t>40240</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56345</t>
+          <t>60363</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>81673</t>
+          <t>88090</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66440</t>
+          <t>73226</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96114</t>
+          <t>105102</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>33773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>38961</t>
+          <t>43074</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30481</t>
+          <t>33885</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48530</t>
+          <t>53074</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>58277</t>
+          <t>65782</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47753</t>
+          <t>53979</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>72367</t>
+          <t>80676</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>246856</t>
+          <t>259805</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>246856</t>
+          <t>259805</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>246856</t>
+          <t>259805</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>254034</t>
+          <t>275510</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>254034</t>
+          <t>275510</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>254034</t>
+          <t>275510</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>500890</t>
+          <t>535315</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>500890</t>
+          <t>535315</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>500890</t>
+          <t>535315</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22755</t>
+          <t>26989</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>26918</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>31718</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>25507</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>43354</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -3566,67 +3566,67 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>62184</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51235</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78147</t>
+          <t>85871</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>26,74%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>32,45%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>73552</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>63927</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>86254</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>25,64%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>21,12%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>32,22%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>67614</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>57106</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>78870</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>30,09%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>25,42%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>129798</t>
+          <t>144295</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>113895</t>
+          <t>126353</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>147139</t>
+          <t>161716</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>93710</t>
+          <t>100615</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78632</t>
+          <t>86301</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107156</t>
+          <t>116223</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>78355</t>
+          <t>87726</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67603</t>
+          <t>76338</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89008</t>
+          <t>99777</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>172065</t>
+          <t>188341</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>154272</t>
+          <t>169813</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>189241</t>
+          <t>206761</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>35740</t>
+          <t>39250</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>28760</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>50937</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25131</t>
+          <t>27987</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>32718</t>
+          <t>36069</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>60871</t>
+          <t>67236</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>49418</t>
+          <t>54314</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>74301</t>
+          <t>80863</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>36502</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>47596</t>
+          <t>49488</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>36256</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>32136</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44602</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>72758</t>
+          <t>78885</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>59799</t>
+          <t>66412</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>85518</t>
+          <t>94805</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>242539</t>
+          <t>264592</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>242539</t>
+          <t>264592</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>242539</t>
+          <t>264592</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>224671</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>224671</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>224671</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>467210</t>
+          <t>513956</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>467210</t>
+          <t>513956</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>467210</t>
+          <t>513956</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,27 +4135,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15457</t>
+          <t>17097</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>47448</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>31001</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>51656</t>
+          <t>39615</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>32045</t>
+          <t>34707</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24142</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40447</t>
+          <t>44497</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>258201</t>
+          <t>59092</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>114076</t>
+          <t>49217</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>339643</t>
+          <t>67861</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>290246</t>
+          <t>93799</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>133226</t>
+          <t>81644</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>434118</t>
+          <t>108116</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>59756</t>
+          <t>67354</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>50560</t>
+          <t>57059</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>70360</t>
+          <t>78637</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>48269</t>
+          <t>52773</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>44339</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>113866</t>
+          <t>61881</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>108025</t>
+          <t>120128</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>39873</t>
+          <t>106115</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>185591</t>
+          <t>134601</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>25188</t>
+          <t>28374</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18569</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>37431</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>22045</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>47959</t>
+          <t>28893</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>44847</t>
+          <t>50419</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>79217</t>
+          <t>61733</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>27206</t>
+          <t>29176</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>34893</t>
+          <t>37901</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>24016</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>19661</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>58544</t>
+          <t>33798</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>51222</t>
+          <t>55202</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>45739</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>90524</t>
+          <t>66375</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>153849</t>
+          <t>170052</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>153849</t>
+          <t>170052</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>153849</t>
+          <t>170052</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>369025</t>
+          <t>180497</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>369025</t>
+          <t>180497</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>369025</t>
+          <t>180497</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>522873</t>
+          <t>350549</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>522873</t>
+          <t>350549</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>522873</t>
+          <t>350549</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>15147</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>22139</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>25208</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>30987</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>40067</t>
+          <t>42655</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>34168</t>
+          <t>36652</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>29263</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>42683</t>
+          <t>46859</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>98298</t>
+          <t>104972</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>87905</t>
+          <t>93574</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>108439</t>
+          <t>115731</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>132466</t>
+          <t>141624</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>119729</t>
+          <t>127097</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>145690</t>
+          <t>155757</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>39841</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>28836</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>45570</t>
+          <t>49298</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>45176</t>
+          <t>49447</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>36125</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>53994</t>
+          <t>59328</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>82067</t>
+          <t>89288</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>70183</t>
+          <t>77365</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>94461</t>
+          <t>102601</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>21339</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>22649</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>26259</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>34972</t>
+          <t>39488</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>26985</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>43793</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>19878</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>15550</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26322</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>22214</t>
+          <t>24333</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>16929</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>31991</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>42091</t>
+          <t>45859</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>34411</t>
+          <t>37154</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>51623</t>
+          <t>56166</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>119963</t>
+          <t>130006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>119963</t>
+          <t>130006</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>119963</t>
+          <t>130006</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>202620</t>
+          <t>219292</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>202620</t>
+          <t>219292</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>202620</t>
+          <t>219292</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>322582</t>
+          <t>349298</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>322582</t>
+          <t>349298</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>322582</t>
+          <t>349298</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>128454</t>
+          <t>128215</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>100104</t>
+          <t>102008</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>167002</t>
+          <t>162206</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>72979</t>
+          <t>116416</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>151828</t>
+          <t>158367</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>249995</t>
+          <t>264735</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>195522</t>
+          <t>232760</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>296322</t>
+          <t>303362</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>283343</t>
+          <t>333148</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>252177</t>
+          <t>301118</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>317602</t>
+          <t>368133</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>593006</t>
+          <t>443842</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>439397</t>
+          <t>412819</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>890283</t>
+          <t>477928</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>876349</t>
+          <t>776990</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>709346</t>
+          <t>731268</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1353989</t>
+          <t>823405</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>488377</t>
+          <t>517923</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>452150</t>
+          <t>481749</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>531702</t>
+          <t>558061</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>430735</t>
+          <t>464961</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>278057</t>
+          <t>432223</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>506462</t>
+          <t>494134</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>919112</t>
+          <t>982883</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>692803</t>
+          <t>933651</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1011986</t>
+          <t>1032145</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>184430</t>
+          <t>203344</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>160164</t>
+          <t>176116</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>212122</t>
+          <t>234296</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>173576</t>
+          <t>191067</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>111466</t>
+          <t>169281</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>212570</t>
+          <t>214024</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>358005</t>
+          <t>394411</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>278263</t>
+          <t>364463</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>401916</t>
+          <t>433554</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>157048</t>
+          <t>174468</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>135529</t>
+          <t>152101</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>184790</t>
+          <t>205744</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>182156</t>
+          <t>206400</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>120102</t>
+          <t>185126</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>219843</t>
+          <t>230343</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>339203</t>
+          <t>380868</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>260708</t>
+          <t>351474</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>384272</t>
+          <t>417216</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>1241651</t>
+          <t>1357099</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1241651</t>
+          <t>1357099</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1241651</t>
+          <t>1357099</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>1501014</t>
+          <t>1442790</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1501014</t>
+          <t>1442790</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1501014</t>
+          <t>1442790</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>2742665</t>
+          <t>2799888</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>2742665</t>
+          <t>2799888</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>2742665</t>
+          <t>2799888</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
